--- a/DocBusinessThienAn/KPI/2026.09_KPI_DatHoangQuy.xlsx
+++ b/DocBusinessThienAn/KPI/2026.09_KPI_DatHoangQuy.xlsx
@@ -1597,10 +1597,10 @@
     <t>https://wework.base.vn/tasks?task=11004385</t>
   </si>
   <si>
-    <t>- Triển khai cơ chế gửi nối đuôi dữ liệu và gửi tức thì khi có dữ liệu mới
-- Xử lý luồng gửi dữ liệu: lấy dữ liệu từ CSDL và chuyển đổi đúng cấu trúc đối tác yêu cầu
-- Tự động đóng gói và ghi file dữ liệu gửi đi để lưu trữ làm bằng chứng đối soát
-- Chuẩn hóa luồng log cha - con và theo dõi fix bug kiểm thử F16</t>
+    <t>- Triển khai gửi dữ liệu nối đuôi và truyền nhận tức thì khi có dữ liệu mới
+- Chuyển đổi cấu trúc dữ liệu theo đúng chuẩn đối tác yêu cầu
+- Tự động đóng gói và lưu trữ file dữ liệu đối soát
+- Chuẩn hóa luồng log phục vụ nghiệm thu hệ thống</t>
   </si>
   <si>
     <t>XD001.6.3. Service tích hợp thiết bị</t>
@@ -1609,18 +1609,18 @@
     <t>https://wework.base.vn/tasks?task=11004386</t>
   </si>
   <si>
-    <t>- Nghiên cứu tài liệu chuẩn giao tiếp ISAPI của thiết bị điều khiển màn hình
-- Xây dựng API và cơ chế phân quyền VideoWall theo người dùng, tổ chức và ô màn hình
-- Phát triển Worker Service giao tiếp thiết bị qua ISAPI/NATS
-- Xây dựng form WPF test thiết bị
-- Trực tiếp ra site kiểm thử thiết bị (2 ngày): kiểm tra kết nối phần cứng và điều khiển màn hình tại hiện trường</t>
+    <t>- Nghiên cứu chuẩn giao tiếp thiết bị điều khiển màn hình (ISAPI Hikvision)
+- Xây dựng API và phân quyền điều khiển theo người dùng và khu vực màn hình
+- Phát triển Worker Service kết nối thiết bị qua NATS
+- Xây dựng phần mềm kiểm thử thiết bị (WPF)
+- Trực tiếp ra site kiểm thử và nghiệm thu thiết bị</t>
   </si>
   <si>
     <t>2026-09</t>
   </si>
   <si>
-    <t>- Phân hệ VideoWall (Tìm hiểu &amp; Kiểm thử site): Nghiên cứu tài liệu chuẩn giao tiếp ISAPI (Hikvision) nắm rõ cơ chế điều khiển màn hình; phát triển Worker Service qua NATS điều khiển thiết bị không nghẽn WebAPI, tự làm form WPF test thiết bị và trực tiếp ra site kiểm thử 2 ngày nghiệm thu thành công.
-- Phân hệ ShareData (Thực hiện &amp; Tối ưu): Triển khai cơ chế gửi nối đuôi kết hợp Change Tracking &amp; NATS giúp đẩy dữ liệu tức thì và tối ưu tải CSDL nhanh hơn.</t>
+    <t>- Phân hệ VideoWall: Nghiên cứu chuẩn giao tiếp ISAPI Hikvision; xây dựng API phân quyền điều khiển theo người dùng và khu vực màn hình; phát triển Worker Service chạy nền kết nối thiết bị qua NATS; làm tool WPF kiểm thử và trực tiếp ra site kiểm thử thiết bị nghiệm thu thành công.
+- Phân hệ ShareData: Xây dựng cơ chế gửi nối đuôi và truyền nhận dữ liệu tức thì, tối ưu tải hệ thống; tự động đóng gói lưu trữ file đối soát và chuẩn hóa log phục vụ nghiệm thu hệ thống.</t>
   </si>
 </sst>
 </file>
@@ -10578,7 +10578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:41" s="122" customFormat="1" ht="176.0">
+    <row r="14" spans="1:41" s="122" customFormat="1" ht="160.0">
       <c r="A14" s="333">
         <v>2</v>
       </c>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="L7" s="298"/>
       <c r="M7" s="299">
-        <v>46295</v>
+        <v>46311</v>
       </c>
       <c r="N7" s="300"/>
       <c r="O7" s="301"/>
